--- a/companies.xlsx
+++ b/companies.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>www.beanleafcafé.example.com</t>
+          <t>www.beanleafcafe.example.com</t>
         </is>
       </c>
     </row>
